--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92470</v>
+        <v>92471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>131263749</v>
       </c>
       <c r="B7" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92471</v>
+        <v>92473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96609</v>
+        <v>96611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>131263749</v>
       </c>
       <c r="B7" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92473</v>
+        <v>92474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96611</v>
+        <v>96612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>131263749</v>
       </c>
       <c r="B7" t="n">
-        <v>58264</v>
+        <v>58270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92479</v>
+        <v>92485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96617</v>
+        <v>96623</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92485</v>
+        <v>92486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96623</v>
+        <v>96624</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>131263749</v>
       </c>
       <c r="B7" t="n">
-        <v>58270</v>
+        <v>58271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92486</v>
+        <v>92487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>131263749</v>
       </c>
       <c r="B7" t="n">
-        <v>58271</v>
+        <v>58274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>131263369</v>
       </c>
       <c r="B8" t="n">
-        <v>92487</v>
+        <v>92490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>131302060</v>
       </c>
       <c r="B9" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3578-2026 artfynd.xlsx
+++ b/artfynd/A 3578-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96258021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131302060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103859980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96258093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103859968</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131263369</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131263749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,8 +1582,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103859951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>